--- a/job_application_forms/035_sales_interview_form_with_voice_record--job_application_forms.xlsx
+++ b/job_application_forms/035_sales_interview_form_with_voice_record--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>recording_audio</t>
+          <t>recording_audio_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>recording audio</t>
+          <t>Recording Audio 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>job_location</t>
+          <t>job_location_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>job location</t>
+          <t>Job Location 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>recording_audio</t>
+          <t>recording_audio_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>recording audio</t>
+          <t>Recording Audio 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>recording_audio</t>
+          <t>recording_audio_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>recording audio</t>
+          <t>Recording Audio 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -894,9 +894,9 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'technical'}</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Technical'}</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -992,46 +992,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>recording_audio_choices</t>
+          <t>recording_audio_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>recording_audio_choices</t>
+          <t>recording_audio_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
